--- a/docs/downloads/04/tbl_other_educ_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -388,10 +388,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>27.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="3">
@@ -438,14 +438,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -460,10 +454,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D6">
-        <v>30.1</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7">
@@ -510,32 +504,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>7.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D10">
-        <v>1.5</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +540,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D11">
-        <v>24.1</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="12">
@@ -564,14 +558,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C12">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="D12">
-        <v>42.2</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="13">
@@ -582,50 +576,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C13">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D13">
-        <v>24.7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D14">
-        <v>7.8</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D15">
-        <v>1.2</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="16">
@@ -636,14 +630,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C16">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D16">
-        <v>30.8</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="17">
@@ -654,68 +648,68 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C17">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D17">
-        <v>44.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>17.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="D19">
-        <v>4.1</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D20">
-        <v>2.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="21">
@@ -726,68 +720,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C21">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D21">
-        <v>27.9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C22">
         <v>61</v>
       </c>
       <c r="D22">
-        <v>44.9</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C23">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D23">
-        <v>22.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="D24">
-        <v>4.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="25">
@@ -798,92 +792,92 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C25">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="D25">
-        <v>26.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C26">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="D26">
-        <v>50</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C27">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="D27">
-        <v>16.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C28">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D28">
-        <v>6.9</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D29">
-        <v>0.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -892,16 +886,16 @@
         </is>
       </c>
       <c r="C30">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D30">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -910,16 +904,16 @@
         </is>
       </c>
       <c r="C31">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D31">
-        <v>51.2</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -928,208 +922,100 @@
         </is>
       </c>
       <c r="C32">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D32">
-        <v>13.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C33">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D33">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>356</v>
       </c>
       <c r="D34">
-        <v>0.8</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C35">
-        <v>60</v>
+        <v>677</v>
       </c>
       <c r="D35">
-        <v>27.1</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C36">
-        <v>96</v>
+        <v>285</v>
       </c>
       <c r="D36">
-        <v>43.4</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C37">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="D37">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>12</v>
-      </c>
-      <c r="D38">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>407</v>
-      </c>
-      <c r="D39">
-        <v>27.7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>677</v>
-      </c>
-      <c r="D40">
-        <v>46.1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>285</v>
-      </c>
-      <c r="D41">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>86</v>
-      </c>
-      <c r="D42">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>12</v>
-      </c>
-      <c r="D43">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_educ_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,12 +387,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C2">
-        <v>23</v>
-      </c>
-      <c r="D2">
-        <v>24.5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -402,14 +396,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C3">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>54.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +414,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="5">
@@ -438,26 +432,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>55</v>
-      </c>
-      <c r="D6">
-        <v>26.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -468,14 +462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C7">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>39.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8">
@@ -486,14 +480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="9">
@@ -504,50 +498,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D9">
-        <v>12.1</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C10">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D10">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C11">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>42.2</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="12">
@@ -558,14 +552,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C12">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>24.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -576,68 +570,68 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C14">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D14">
-        <v>28.1</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C15">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D15">
-        <v>44.5</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C16">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16">
-        <v>17.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -648,38 +642,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C18">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D18">
-        <v>19.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -688,16 +682,16 @@
         </is>
       </c>
       <c r="C19">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D19">
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -706,16 +700,16 @@
         </is>
       </c>
       <c r="C20">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D20">
-        <v>22.8</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -724,16 +718,16 @@
         </is>
       </c>
       <c r="C21">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -742,279 +736,441 @@
         </is>
       </c>
       <c r="C22">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>24.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C23">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>50</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C24">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D24">
-        <v>16.1</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C25">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D25">
-        <v>9.300000000000001</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C26">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D26">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C27">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>51.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C28">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D28">
-        <v>13.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="D29">
-        <v>10.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C30">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D30">
-        <v>24</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C31">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="D31">
-        <v>43.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C32">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D32">
-        <v>24</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C33">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D33">
-        <v>8.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C34">
-        <v>356</v>
+        <v>128</v>
       </c>
       <c r="D34">
-        <v>24.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C35">
-        <v>677</v>
+        <v>34</v>
       </c>
       <c r="D35">
-        <v>46.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C36">
-        <v>285</v>
+        <v>27</v>
       </c>
       <c r="D36">
-        <v>19.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>17</v>
+      </c>
+      <c r="D37">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>96</v>
+      </c>
+      <c r="D39">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>53</v>
+      </c>
+      <c r="D40">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>19</v>
+      </c>
+      <c r="D41">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>85</v>
+      </c>
+      <c r="D42">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>271</v>
+      </c>
+      <c r="D43">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>677</v>
+      </c>
+      <c r="D44">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>285</v>
+      </c>
+      <c r="D45">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="C37">
+      <c r="C46">
         <v>149</v>
       </c>
-      <c r="D37">
+      <c r="D46">
         <v>10.2</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_other_educ_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -457,7 +457,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
